--- a/cds_files/TexasTech_CDS_2021-2022.xlsx
+++ b/cds_files/TexasTech_CDS_2021-2022.xlsx
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.89</v>
+        <v>0.908</v>
       </c>
       <c r="C3" t="n">
-        <v>0.23</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.11</v>
+        <v>0.092</v>
       </c>
       <c r="C4" t="n">
-        <v>0.77</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +525,7 @@
         <v>0.09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09</v>
+        <v>0.067</v>
       </c>
     </row>
   </sheetData>
